--- a/credentials/Credentials_TJKT 2.xlsx
+++ b/credentials/Credentials_TJKT 2.xlsx
@@ -397,13 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +412,9 @@
       <c r="D1" t="str">
         <v>Password</v>
       </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -432,6 +429,9 @@
       <c r="D2" t="str">
         <v>123456</v>
       </c>
+      <c r="E2" t="str">
+        <v>jkt20238044.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -446,6 +446,9 @@
       <c r="D3" t="str">
         <v>123456</v>
       </c>
+      <c r="E3" t="str">
+        <v>jkt20238047.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -460,6 +463,9 @@
       <c r="D4" t="str">
         <v>123456</v>
       </c>
+      <c r="E4" t="str">
+        <v>jkt20238074.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -474,6 +480,9 @@
       <c r="D5" t="str">
         <v>123456</v>
       </c>
+      <c r="E5" t="str">
+        <v>jkt20238080.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -488,6 +497,9 @@
       <c r="D6" t="str">
         <v>123456</v>
       </c>
+      <c r="E6" t="str">
+        <v>jkt20238089.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -502,6 +514,9 @@
       <c r="D7" t="str">
         <v>123456</v>
       </c>
+      <c r="E7" t="str">
+        <v>jkt20238103.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -516,6 +531,9 @@
       <c r="D8" t="str">
         <v>123456</v>
       </c>
+      <c r="E8" t="str">
+        <v>jkt20238137.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -530,6 +548,9 @@
       <c r="D9" t="str">
         <v>123456</v>
       </c>
+      <c r="E9" t="str">
+        <v>jkt20238154.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -544,6 +565,9 @@
       <c r="D10" t="str">
         <v>123456</v>
       </c>
+      <c r="E10" t="str">
+        <v>jkt20238191.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -558,6 +582,9 @@
       <c r="D11" t="str">
         <v>123456</v>
       </c>
+      <c r="E11" t="str">
+        <v>jkt20238208.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -572,6 +599,9 @@
       <c r="D12" t="str">
         <v>123456</v>
       </c>
+      <c r="E12" t="str">
+        <v>jkt20238235.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -586,6 +616,9 @@
       <c r="D13" t="str">
         <v>123456</v>
       </c>
+      <c r="E13" t="str">
+        <v>jkt20238238.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -600,6 +633,9 @@
       <c r="D14" t="str">
         <v>123456</v>
       </c>
+      <c r="E14" t="str">
+        <v>jkt20238242.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -614,6 +650,9 @@
       <c r="D15" t="str">
         <v>123456</v>
       </c>
+      <c r="E15" t="str">
+        <v>jkt20238300.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -628,6 +667,9 @@
       <c r="D16" t="str">
         <v>123456</v>
       </c>
+      <c r="E16" t="str">
+        <v>jkt20238301.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -642,6 +684,9 @@
       <c r="D17" t="str">
         <v>123456</v>
       </c>
+      <c r="E17" t="str">
+        <v>jkt20238309.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -656,6 +701,9 @@
       <c r="D18" t="str">
         <v>123456</v>
       </c>
+      <c r="E18" t="str">
+        <v>jkt20238319.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -670,6 +718,9 @@
       <c r="D19" t="str">
         <v>123456</v>
       </c>
+      <c r="E19" t="str">
+        <v>jkt20238329.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -684,6 +735,9 @@
       <c r="D20" t="str">
         <v>123456</v>
       </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -698,6 +752,9 @@
       <c r="D21" t="str">
         <v>123456</v>
       </c>
+      <c r="E21" t="str">
+        <v>jkt20238361.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -712,6 +769,9 @@
       <c r="D22" t="str">
         <v>123456</v>
       </c>
+      <c r="E22" t="str">
+        <v>jkt20238385.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -726,6 +786,9 @@
       <c r="D23" t="str">
         <v>123456</v>
       </c>
+      <c r="E23" t="str">
+        <v>jkt20238396.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -740,6 +803,9 @@
       <c r="D24" t="str">
         <v>123456</v>
       </c>
+      <c r="E24" t="str">
+        <v>jkt20238426.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -754,6 +820,9 @@
       <c r="D25" t="str">
         <v>123456</v>
       </c>
+      <c r="E25" t="str">
+        <v>jkt20238470.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -768,6 +837,9 @@
       <c r="D26" t="str">
         <v>123456</v>
       </c>
+      <c r="E26" t="str">
+        <v>jkt20238486.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -782,6 +854,9 @@
       <c r="D27" t="str">
         <v>123456</v>
       </c>
+      <c r="E27" t="str">
+        <v>jkt20238500.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -796,6 +871,9 @@
       <c r="D28" t="str">
         <v>123456</v>
       </c>
+      <c r="E28" t="str">
+        <v>jkt20238525.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -810,6 +888,9 @@
       <c r="D29" t="str">
         <v>123456</v>
       </c>
+      <c r="E29" t="str">
+        <v>jkt20238548.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -824,6 +905,9 @@
       <c r="D30" t="str">
         <v>123456</v>
       </c>
+      <c r="E30" t="str">
+        <v>jkt20238559.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -838,6 +922,9 @@
       <c r="D31" t="str">
         <v>123456</v>
       </c>
+      <c r="E31" t="str">
+        <v>jkt20238572.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -852,6 +939,9 @@
       <c r="D32" t="str">
         <v>123456</v>
       </c>
+      <c r="E32" t="str">
+        <v>jkt20238602.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -866,6 +956,9 @@
       <c r="D33" t="str">
         <v>123456</v>
       </c>
+      <c r="E33" t="str">
+        <v>jkt20238604.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -880,6 +973,9 @@
       <c r="D34" t="str">
         <v>123456</v>
       </c>
+      <c r="E34" t="str">
+        <v>jkt20238608.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -894,6 +990,9 @@
       <c r="D35" t="str">
         <v>123456</v>
       </c>
+      <c r="E35" t="str">
+        <v>jkt20238610.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -908,10 +1007,13 @@
       <c r="D36" t="str">
         <v>123456</v>
       </c>
+      <c r="E36" t="str">
+        <v>jkt20238624.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>